--- a/outputs/cricsheet_player_names.xlsx
+++ b/outputs/cricsheet_player_names.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,16 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B201"/>
+  <dimension ref="A1:B204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
@@ -683,199 +671,199 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Arshad Khan</t>
+          <t>Arjun Tendulkar</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Arshdeep Singh</t>
+          <t>Arshad Khan</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ashok Sharma</t>
+          <t>Arshdeep Singh</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ashutosh Sharma</t>
+          <t>Ashok Sharma</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ashwani Kumar</t>
+          <t>Ashutosh Sharma</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Auqib Nabi</t>
+          <t>Ashwani Kumar</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Avesh Khan</t>
+          <t>Auqib Nabi</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lucknow Super Giants</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Azmatullah Omarzai</t>
+          <t>Avesh Khan</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B Kumar</t>
+          <t>Azmatullah Omarzai</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B Muzarabani</t>
+          <t>B Kumar</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kolkata Knight Riders</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B Sai Sudharsan</t>
+          <t>B Muzarabani</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BJ Dwarshuis</t>
+          <t>B Sai Sudharsan</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brijesh Sharma</t>
+          <t>BJ Dwarshuis</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C Bosch</t>
+          <t>Brijesh Sharma</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C Connolly</t>
+          <t>C Bosch</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C Green</t>
+          <t>C Connolly</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kolkata Knight Riders</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CV Varun</t>
+          <t>C Green</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -887,535 +875,535 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>D Brevis</t>
+          <t>CV Varun</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>D Ferreira</t>
+          <t>D Brevis</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>D Madushanka</t>
+          <t>D Ferreira</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>D Padikkal</t>
+          <t>D Madushanka</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DA Miller</t>
+          <t>D Padikkal</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DA Payne</t>
+          <t>DA Miller</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DL Chahar</t>
+          <t>DA Payne</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DS Rathi</t>
+          <t>DL Chahar</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lucknow Super Giants</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DV Malewar</t>
+          <t>DS Rathi</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dhruv Jurel</t>
+          <t>DV Malewar</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>E Malinga</t>
+          <t>Dhruv Jurel</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FH Allen</t>
+          <t>E Malinga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kolkata Knight Riders</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GD Phillips</t>
+          <t>FH Allen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GF Linde</t>
+          <t>GD Phillips</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lucknow Super Giants</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Gurjapneet Singh</t>
+          <t>GF Linde</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>H Klaasen</t>
+          <t>Gurjapneet Singh</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HH Pandya</t>
+          <t>H Klaasen</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HV Patel</t>
+          <t>HH Pandya</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Harpreet Brar</t>
+          <t>HV Patel</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Harsh Dubey</t>
+          <t>Harpreet Brar</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Himmat Singh</t>
+          <t>Harsh Dubey</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lucknow Super Giants</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ishan Kishan</t>
+          <t>Himmat Singh</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>J Overton</t>
+          <t>Ishan Kishan</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JA Duffy</t>
+          <t>J Overton</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JC Archer</t>
+          <t>JA Duffy</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JC Buttler</t>
+          <t>JC Archer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JD Unadkat</t>
+          <t>JC Buttler</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>JG Bethell</t>
+          <t>JD Unadkat</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>JJ Bumrah</t>
+          <t>JG Bethell</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>JM Sharma</t>
+          <t>JJ Bumrah</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>JO Holder</t>
+          <t>JM Cox</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>JP Inglis</t>
+          <t>JM Sharma</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lucknow Super Giants</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>JR Hazlewood</t>
+          <t>JO Holder</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>K Rabada</t>
+          <t>JP Inglis</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KA Jamieson</t>
+          <t>JR Hazlewood</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KH Pandya</t>
+          <t>K Rabada</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>KK Ahmed</t>
+          <t>KA Jamieson</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KK Nair</t>
+          <t>KH Pandya</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KL Rahul</t>
+          <t>KK Ahmed</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kartik Sharma</t>
+          <t>KK Nair</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kartik Tyagi</t>
+          <t>KL Rahul</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Kolkata Knight Riders</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Krish Bhagat</t>
+          <t>Kartik Sharma</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kuldeep Yadav</t>
+          <t>Kartik Tyagi</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kumar Kushagra</t>
+          <t>Krish Bhagat</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>L Ngidi</t>
+          <t>Kuldeep Yadav</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1427,43 +1415,43 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>LG Pretorius</t>
+          <t>Kumar Kushagra</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LH Ferguson</t>
+          <t>L Ngidi</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LS Livingstone</t>
+          <t>LG Pretorius</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>M Jansen</t>
+          <t>LH Ferguson</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -1475,247 +1463,247 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>M Markande</t>
+          <t>LS Livingstone</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>M Pathirana</t>
+          <t>M Jansen</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Kolkata Knight Riders</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>M Prasidh Krishna</t>
+          <t>M Markande</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>M Shahrukh Khan</t>
+          <t>M Pathirana</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>M Siddharth</t>
+          <t>M Prasidh Krishna</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lucknow Super Giants</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>M Tiwari</t>
+          <t>M Shahrukh Khan</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MA Starc</t>
+          <t>M Siddharth</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MD Choudhary</t>
+          <t>M Tiwari</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lucknow Super Giants</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MD Shanaka</t>
+          <t>MA Starc</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MJ Henry</t>
+          <t>MD Choudhary</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MJ Santner</t>
+          <t>MD Shanaka</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MJ Suthar</t>
+          <t>MJ Henry</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MK Pandey</t>
+          <t>MJ Santner</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Kolkata Knight Riders</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MP Stoinis</t>
+          <t>MJ Suthar</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MP Yadav</t>
+          <t>MK Pandey</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lucknow Super Giants</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MR Marsh</t>
+          <t>MP Stoinis</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lucknow Super Giants</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MW Short</t>
+          <t>MP Yadav</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Mayank Rawat</t>
+          <t>MR Marsh</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Mohammed Shami</t>
+          <t>MW Short</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lucknow Super Giants</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Mohammed Siraj</t>
+          <t>Mayank Rawat</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Mohsin Khan</t>
+          <t>Mohammed Shami</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -1727,163 +1715,163 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Mukesh Choudhary</t>
+          <t>Mohammed Siraj</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Mukesh Kumar</t>
+          <t>Mohsin Khan</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>N Burger</t>
+          <t>Mukesh Choudhary</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>N Pooran</t>
+          <t>Mukesh Kumar</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Lucknow Super Giants</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>N Rana</t>
+          <t>N Burger</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>N Sindhu</t>
+          <t>N Pooran</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>N Wadhera</t>
+          <t>N Rana</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Naman Dhir</t>
+          <t>N Sindhu</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Navdeep Saini</t>
+          <t>N Wadhera</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Kolkata Knight Riders</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Nithish Kumar Reddy</t>
+          <t>Naman Dhir</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Navdeep Saini</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>P Dubey</t>
+          <t>Nithish Kumar Reddy</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>P Nissanka</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>P Simran Singh</t>
+          <t>P Dubey</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -1895,427 +1883,427 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PD Salt</t>
+          <t>P Nissanka</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PJ Cummins</t>
+          <t>P Simran Singh</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PP Hinge</t>
+          <t>PD Salt</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PR Veer</t>
+          <t>PJ Cummins</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PVD Chameera</t>
+          <t>PP Hinge</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Prince Yadav</t>
+          <t>PR Veer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Lucknow Super Giants</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Priyansh Arya</t>
+          <t>PVD Chameera</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Q de Kock</t>
+          <t>Prince Yadav</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>R Minz</t>
+          <t>Priyansh Arya</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>R Parag</t>
+          <t>Q de Kock</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>R Powell</t>
+          <t>R Minz</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Kolkata Knight Riders</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>R Sai Kishore</t>
+          <t>R Parag</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>R Shepherd</t>
+          <t>R Powell</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>R Smaran</t>
+          <t>R Sai Kishore</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>R Tewatia</t>
+          <t>R Shepherd</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>RA Bawa</t>
+          <t>R Smaran</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>RA Jadeja</t>
+          <t>R Tewatia</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>RD Chahar</t>
+          <t>RA Bawa</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RD Gaikwad</t>
+          <t>RA Jadeja</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RD Rickelton</t>
+          <t>RD Chahar</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RG Sharma</t>
+          <t>RD Gaikwad</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RK Singh</t>
+          <t>RD Rickelton</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Kolkata Knight Riders</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RM Patidar</t>
+          <t>RG Sharma</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>RR Pant</t>
+          <t>RK Singh</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Lucknow Super Giants</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RS Ghosh</t>
+          <t>RM Patidar</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Raghu Sharma</t>
+          <t>RR Pant</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ramandeep Singh</t>
+          <t>RS Ghosh</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Kolkata Knight Riders</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Raghu Sharma</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Rasikh Salam</t>
+          <t>Ramandeep Singh</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ravi Bishnoi</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ravi Singh</t>
+          <t>Rasikh Salam</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>S Arora</t>
+          <t>Ravi Bishnoi</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>S Dube</t>
+          <t>Ravi Singh</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SA Yadav</t>
+          <t>S Arora</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SB Dubey</t>
+          <t>S Dube</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SE Rutherford</t>
+          <t>SA Yadav</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -2327,463 +2315,463 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SH Johnson</t>
+          <t>SB Dubey</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SN Khan</t>
+          <t>SE Rutherford</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SN Thakur</t>
+          <t>SH Johnson</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SO Hetmyer</t>
+          <t>SN Khan</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SP Narine</t>
+          <t>SN Thakur</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Kolkata Knight Riders</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SR Dubey</t>
+          <t>SO Hetmyer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Kolkata Knight Riders</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SS Iyer</t>
+          <t>SP Narine</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SS Mishra</t>
+          <t>SR Dubey</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SU Parakh</t>
+          <t>SS Iyer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SV Samson</t>
+          <t>SS Mishra</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Sakib Hussain</t>
+          <t>SU Parakh</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Sameer Rizvi</t>
+          <t>SV Samson</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Sandeep Sharma</t>
+          <t>Sakib Hussain</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Shahbaz Ahmed</t>
+          <t>Sameer Rizvi</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Lucknow Super Giants</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Shashank Singh</t>
+          <t>Sandeep Sharma</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Shivang Kumar</t>
+          <t>Shahbaz Ahmed</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Lucknow Super Giants</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Shubman Gill</t>
+          <t>Shashank Singh</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Suryansh Shedge</t>
+          <t>Shivang Kumar</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Suyash Sharma</t>
+          <t>Shubman Gill</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>T Natarajan</t>
+          <t>Suryansh Shedge</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>T Stubbs</t>
+          <t>Suyash Sharma</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>T Vijay</t>
+          <t>T Dahiya</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TA Boult</t>
+          <t>T Natarajan</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TH David</t>
+          <t>T Stubbs</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TL Seifert</t>
+          <t>T Vijay</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Kolkata Knight Riders</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TM Head</t>
+          <t>TA Boult</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Sunrisers Hyderabad</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>TU Deshpande</t>
+          <t>TH David</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Tilak Varma</t>
+          <t>TL Seifert</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Urvil Patel</t>
+          <t>TM Head</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Chennai Super Kings</t>
+          <t>Sunrisers Hyderabad</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>V Kohli</t>
+          <t>TU Deshpande</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>V Nigam</t>
+          <t>Tilak Varma</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Delhi Capitals</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>V Suryavanshi</t>
+          <t>Urvil Patel</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Chennai Super Kings</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>VG Arora</t>
+          <t>V Kohli</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Kolkata Knight Riders</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>VR Iyer</t>
+          <t>V Nigam</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Royal Challengers Bengaluru</t>
+          <t>Delhi Capitals</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Vijaykumar Vyshak</t>
+          <t>V Suryavanshi</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Rajasthan Royals</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Vishnu Vinod</t>
+          <t>VG Arora</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Kolkata Knight Riders</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>WG Jacks</t>
+          <t>VR Iyer</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Mumbai Indians</t>
+          <t>Royal Challengers Bengaluru</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Washington Sundar</t>
+          <t>Vijaykumar Vyshak</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Gujarat Titans</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>XC Bartlett</t>
+          <t>Vishnu Vinod</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -2795,46 +2783,82 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>YBK Jaiswal</t>
+          <t>WG Jacks</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Mumbai Indians</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>YS Chahal</t>
+          <t>Washington Sundar</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Punjab Kings</t>
+          <t>Gujarat Titans</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Yash Raj Punja</t>
+          <t>XC Bartlett</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Rajasthan Royals</t>
+          <t>Punjab Kings</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
+          <t>YBK Jaiswal</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Rajasthan Royals</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>YS Chahal</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Punjab Kings</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Yash Raj Punja</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Rajasthan Royals</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
           <t>Yash Thakur</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>Punjab Kings</t>
         </is>
